--- a/history_prices/APR/prices_24042026.xlsx
+++ b/history_prices/APR/prices_24042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\APR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF98A4E-C5F5-40DF-A830-20FA848EBA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8565BD-3F5B-49F4-A1C2-B9A3F4898768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1332,9 +1332,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.00_-"/>
-    <numFmt numFmtId="167" formatCode="&quot;€&quot;#,##0.000_-"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="&quot;€&quot;#,##0.00_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.000_-"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -1367,9 +1367,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
